--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="469">
   <si>
     <t>ID</t>
   </si>
@@ -108,7 +108,49 @@
     <t>charfadein(L,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_Abaddon; 层级=1; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_Abaddon; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>5</t>
@@ -477,7 +519,25 @@
     <t>可即便如此，身为探员的敏锐还是让你迅速从中捕捉到了几个关键点——1、眼前有着盖曼外表的男人并不是当初那个盖曼.阿门努斯。2、纳丁达克公司很可能利用盖曼做了些什么，而且是他当年失踪案的元凶。</t>
   </si>
   <si>
-    <t>loadScript(克拉克线4层（终）_1, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_clark4F(4)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 1)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=40; gotomainline= 克拉克线4层（终）_1</t>
@@ -571,6 +631,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadein(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -895,72 +960,88 @@
     <t>反应很快，不愧是久经训练的探员。所以现在，你们应该知道我的好学生跟你们走这一趟背后到底打得什么算盘了吧。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Abaddon; 层级=25; gotomainline= 克拉克线4层（终）_1</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=15</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>不，她已经说得足够多了，关于这所医院的过去，关于造梦设备，还有关于你的事情。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=16; tag=相信索菲亚</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>你回握住索菲亚柔软的手指，眼神坚定地挡在她的身前。虽然你能感觉到她并未将所有事实和盘托出，但这并不是听信亚波伦的挑拨，而将她也当做敌人对待的理由。</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>是吗？那为什么连我这个事件的当事人，都对她口中的一些细节有些不敢苟同呢？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=18</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>你窃听了我们谈话？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=19</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>克拉克警惕地扫视了一圈房间，并没有以肉眼发现任何监听设备的迹象，当时发生这段对话的场景是在外面的走廊，他不可能让自己的耳目遍布这里的每一个角落。</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>或许我只是了解自己的学生，知道她会如何把混合了真相的谎言做成美味的糖饼，喂给两个心甘情愿被她牵着鼻子走的纯情大男孩罢了。</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>够了，如果你没有任何可以辩驳的点，就乖乖闭上嘴，提出你的条件。或是在我们决定鱼死网破之前，把大卫放了。</t>
-  </si>
-  <si>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_clark4F(4),</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=25; gotomainline= 克拉克线4层（终）_1</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=15</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>不，她已经说得足够多了，关于这所医院的过去，关于造梦设备，还有关于你的事情。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=16; tag=相信索菲亚</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>你回握住索菲亚柔软的手指，眼神坚定地挡在她的身前。虽然你能感觉到她并未将所有事实和盘托出，但这并不是听信亚波伦的挑拨，而将她也当做敌人对待的理由。</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>是吗？那为什么连我这个事件的当事人，都对她口中的一些细节有些不敢苟同呢？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=18</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>你窃听了我们谈话？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=19</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>克拉克警惕地扫视了一圈房间，并没有以肉眼发现任何监听设备的迹象，当时发生这段对话的场景是在外面的走廊，他不可能让自己的耳目遍布这里的每一个角落。</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>或许我只是了解自己的学生，知道她会如何把混合了真相的谎言做成美味的糖饼，喂给两个心甘情愿被她牵着鼻子走的纯情大男孩罢了。</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>够了，如果你没有任何可以辩驳的点，就乖乖闭上嘴，提出你的条件。或是在我们决定鱼死网破之前，把大卫放了。</t>
+  </si>
+  <si>
+    <r>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -969,7 +1050,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>克拉克线</t>
+      <t>sntzm_clark4F(4)</t>
     </r>
     <r>
       <rPr>
@@ -977,23 +1058,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层（终）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_1, 1)</t>
+      <t>, 1)</t>
     </r>
   </si>
   <si>
@@ -2191,10 +2256,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2853,7 +2918,7 @@
       <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4332,7 +4397,7 @@
       <c r="J42" t="s">
         <v>15</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="3" t="s">
         <v>147</v>
       </c>
       <c r="L42" t="s">
@@ -4712,10 +4777,10 @@
       <c r="J52" t="s">
         <v>15</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K52" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="2" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6039,16 +6104,16 @@
       <c r="J87" t="s">
         <v>15</v>
       </c>
-      <c r="K87" t="s">
-        <v>147</v>
+      <c r="K87" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="L87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
@@ -6081,12 +6146,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6104,7 +6169,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6119,12 +6184,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6142,7 +6207,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6162,7 +6227,7 @@
     </row>
     <row r="91" ht="27" spans="1:12">
       <c r="A91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6180,7 +6245,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6195,12 +6260,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" t="s">
         <v>59</v>
@@ -6218,7 +6283,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6233,12 +6298,12 @@
         <v>23</v>
       </c>
       <c r="L92" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="93" ht="54" spans="1:12">
       <c r="A93" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6256,7 +6321,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6276,7 +6341,7 @@
     </row>
     <row r="94" ht="40.5" spans="1:12">
       <c r="A94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
@@ -6294,7 +6359,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6314,7 +6379,7 @@
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
@@ -6332,7 +6397,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6343,11 +6408,11 @@
       <c r="J95" t="s">
         <v>15</v>
       </c>
-      <c r="K95" s="2" t="s">
-        <v>290</v>
+      <c r="K95" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="L95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -6368,31 +6433,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B4" t="s">
         <v>139</v>
@@ -6400,7 +6465,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6408,7 +6473,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -6416,7 +6481,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B7" t="s">
         <v>198</v>
@@ -6424,7 +6489,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
@@ -6432,7 +6497,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
         <v>180</v>
@@ -6440,50 +6505,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6505,616 +6570,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F15" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B18" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B20" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D20" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E20" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F20" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B21" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F21" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B22" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C22" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E22" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F22" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B23" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E23" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B24" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E24" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F24" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E25" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F25" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B26" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D26" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F26" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E28" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F28" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B29" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C29" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C30" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D30" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E30" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F30" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B31" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C31" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11730"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="474">
   <si>
     <t>ID</t>
   </si>
@@ -109,6 +109,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -192,6 +197,9 @@
     <t>“噗呲......”</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=5</t>
   </si>
   <si>
@@ -222,6 +230,9 @@
     <t>没等你来得及发出一句疑问，两张屏幕上便各自闪出一只人影，它们就像后台准备就绪的演员，在观众目光就位的那一刻准时出现在属于自己的位置——</t>
   </si>
   <si>
+    <t>18 enhanced_APPLE</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=8</t>
   </si>
   <si>
@@ -345,6 +356,9 @@
     <t>控制？这个词用的实在有失水准，海尔特探员。曾经，的确有人要求我做这样的事情——把这些病人当成可以随意摆弄的木偶，把他们的脑子拆开，再往里面塞满火药和弹片......</t>
   </si>
   <si>
+    <t>16 enhanced_suspence</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=21</t>
   </si>
   <si>
@@ -520,6 +534,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -598,6 +617,9 @@
   </si>
   <si>
     <t>看到房间中央的两个按钮了吗？</t>
+  </si>
+  <si>
+    <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
     <t>源类型=type:txt_Abaddon; 层级=41</t>
@@ -777,6 +799,9 @@
     <t>你转头一看，这才注意到索菲亚从始至终都没有进入房间的深处，她只是扶着冰冷的门框，既不敢靠近，也没有悄声离开。像被钉住了双腿，一动不动地伫立在门旁的角落里。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>26</t>
   </si>
   <si>
@@ -961,6 +986,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1042,6 +1072,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -3062,7 +3097,7 @@
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
@@ -3071,12 +3106,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3094,7 +3129,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3106,15 +3141,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -3132,7 +3167,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3147,12 +3182,12 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="55.5" spans="1:12">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3170,13 +3205,13 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -3185,12 +3220,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3208,7 +3243,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3223,12 +3258,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3261,12 +3296,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="90" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3284,7 +3319,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3296,24 +3331,24 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3322,7 +3357,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3337,12 +3372,12 @@
         <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3351,7 +3386,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3360,7 +3395,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3375,12 +3410,12 @@
         <v>28</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3398,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3413,12 +3448,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="54" spans="1:12">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3436,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3451,12 +3486,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3489,12 +3524,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="90" spans="1:12">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3512,7 +3547,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3524,24 +3559,24 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:12">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3550,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3565,12 +3600,12 @@
         <v>23</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:12">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3579,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3588,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3603,12 +3638,12 @@
         <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="55.5" spans="1:12">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3626,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3641,12 +3676,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" ht="57" spans="1:12">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
@@ -3664,13 +3699,13 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -3679,15 +3714,15 @@
         <v>23</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3699,10 +3734,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3714,15 +3749,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
@@ -3737,10 +3772,10 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3752,15 +3787,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3778,7 +3813,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3793,12 +3828,12 @@
         <v>28</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
@@ -3816,7 +3851,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3831,15 +3866,15 @@
         <v>23</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:12">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3851,10 +3886,10 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3866,15 +3901,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3889,10 +3924,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3904,15 +3939,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:12">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
@@ -3930,7 +3965,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3945,12 +3980,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3968,7 +4003,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3983,12 +4018,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:12">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
@@ -4006,7 +4041,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4021,12 +4056,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:12">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
@@ -4044,7 +4079,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4059,12 +4094,12 @@
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4082,7 +4117,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4097,12 +4132,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" ht="42" spans="1:12">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
         <v>20</v>
@@ -4120,7 +4155,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4135,12 +4170,12 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4173,12 +4208,12 @@
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="90" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4196,7 +4231,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4211,12 +4246,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
@@ -4234,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4249,12 +4284,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
@@ -4272,7 +4307,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4287,12 +4322,12 @@
         <v>23</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:12">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
@@ -4310,7 +4345,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4325,12 +4360,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4348,7 +4383,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4363,12 +4398,12 @@
         <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4386,7 +4421,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4398,15 +4433,15 @@
         <v>15</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="90" spans="1:12">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
@@ -4424,7 +4459,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4439,12 +4474,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4462,7 +4497,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4477,12 +4512,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4500,7 +4535,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4515,12 +4550,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
@@ -4538,7 +4573,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4553,12 +4588,12 @@
         <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -4576,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4591,12 +4626,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4614,14 +4649,12 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
       </c>
-      <c r="I48" t="s">
-        <v>15</v>
-      </c>
+      <c r="I48"/>
       <c r="J48" t="s">
         <v>15</v>
       </c>
@@ -4629,12 +4662,12 @@
         <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -4652,13 +4685,13 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="J49" t="s">
         <v>15</v>
@@ -4667,12 +4700,12 @@
         <v>23</v>
       </c>
       <c r="L49" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
@@ -4690,7 +4723,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4702,15 +4735,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4728,7 +4761,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4743,12 +4776,12 @@
         <v>28</v>
       </c>
       <c r="L51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" ht="55.5" spans="1:12">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
@@ -4766,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4778,15 +4811,15 @@
         <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" ht="90" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4804,7 +4837,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4816,15 +4849,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" ht="150" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4842,7 +4875,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4854,24 +4887,24 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L54" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4880,7 +4913,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4895,12 +4928,12 @@
         <v>23</v>
       </c>
       <c r="L55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4909,7 +4942,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4918,7 +4951,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4933,12 +4966,12 @@
         <v>28</v>
       </c>
       <c r="L56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" ht="54" spans="1:12">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4956,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4968,15 +5001,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L57" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" ht="150" spans="1:12">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4994,7 +5027,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5006,24 +5039,24 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L58" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5032,7 +5065,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5047,12 +5080,12 @@
         <v>23</v>
       </c>
       <c r="L59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5061,7 +5094,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5070,7 +5103,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5085,12 +5118,12 @@
         <v>28</v>
       </c>
       <c r="L60" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5108,7 +5141,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5120,15 +5153,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L61" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" ht="210" spans="1:12">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
@@ -5146,7 +5179,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5158,15 +5191,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L62" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
@@ -5184,7 +5217,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5199,12 +5232,12 @@
         <v>17</v>
       </c>
       <c r="L63" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
@@ -5222,13 +5255,13 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J64" t="s">
         <v>15</v>
@@ -5242,7 +5275,7 @@
     </row>
     <row r="65" ht="54" spans="1:12">
       <c r="A65" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5260,13 +5293,13 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="J65" t="s">
         <v>15</v>
@@ -5280,7 +5313,7 @@
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
@@ -5298,7 +5331,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5313,12 +5346,12 @@
         <v>23</v>
       </c>
       <c r="L66" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5336,7 +5369,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5351,12 +5384,12 @@
         <v>28</v>
       </c>
       <c r="L67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
@@ -5374,7 +5407,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5389,12 +5422,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5412,7 +5445,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5427,12 +5460,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
@@ -5450,7 +5483,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5465,12 +5498,12 @@
         <v>23</v>
       </c>
       <c r="L70" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
@@ -5488,7 +5521,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5503,12 +5536,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5526,7 +5559,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5541,21 +5574,21 @@
         <v>28</v>
       </c>
       <c r="L72" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B73" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5564,7 +5597,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5579,12 +5612,12 @@
         <v>23</v>
       </c>
       <c r="L73" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5593,7 +5626,7 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5602,7 +5635,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5617,12 +5650,12 @@
         <v>28</v>
       </c>
       <c r="L74" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5640,7 +5673,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5655,12 +5688,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5690,15 +5723,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L76" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5731,12 +5764,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5754,7 +5787,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5769,12 +5802,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5792,7 +5825,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5807,12 +5840,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
         <v>26</v>
@@ -5830,7 +5863,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5845,12 +5878,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" ht="55.5" spans="1:12">
       <c r="A81" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B81" t="s">
         <v>20</v>
@@ -5868,7 +5901,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5883,12 +5916,12 @@
         <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:12">
       <c r="A82" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5906,7 +5939,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5918,15 +5951,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L82" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" ht="55.5" spans="1:12">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
@@ -5944,7 +5977,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5956,12 +5989,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B84" t="s">
         <v>26</v>
@@ -5979,7 +6012,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5994,12 +6027,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6017,7 +6050,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6032,12 +6065,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86" ht="57" spans="1:12">
       <c r="A86" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6055,7 +6088,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6070,12 +6103,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
@@ -6093,7 +6126,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6105,15 +6138,15 @@
         <v>15</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="L87" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
@@ -6146,12 +6179,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6169,7 +6202,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6184,12 +6217,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6207,7 +6240,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6222,15 +6255,15 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="91" ht="27" spans="1:12">
       <c r="A91" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -6245,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6260,21 +6293,21 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6283,7 +6316,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6298,12 +6331,12 @@
         <v>23</v>
       </c>
       <c r="L92" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="93" ht="54" spans="1:12">
       <c r="A93" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6312,7 +6345,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6321,7 +6354,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6336,12 +6369,12 @@
         <v>28</v>
       </c>
       <c r="L93" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" ht="40.5" spans="1:12">
       <c r="A94" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
@@ -6359,7 +6392,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6374,12 +6407,12 @@
         <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
@@ -6397,7 +6430,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6409,10 +6442,10 @@
         <v>15</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="L95" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -6433,39 +6466,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6473,7 +6506,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -6481,74 +6514,74 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B11" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B12" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B13" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -6570,616 +6603,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E4" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F5" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D6" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F6" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E7" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F8" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D9" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E9" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F9" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D10" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E10" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B11" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E11" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F11" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B12" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C12" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D12" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E12" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F12" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B13" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C13" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D13" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E13" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F13" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B15" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C15" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D15" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E15" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F15" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B16" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C16" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D16" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E16" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F16" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B17" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C17" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D17" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F17" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B18" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C18" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D18" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E18" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F18" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B19" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C19" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D19" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E19" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F19" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B20" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C20" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D20" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E20" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F20" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B21" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C21" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D21" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E21" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F21" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C22" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E22" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F22" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B23" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C23" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D23" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E23" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F23" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B24" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D24" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E24" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F24" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B25" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D25" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E25" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F25" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B26" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C26" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D26" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E26" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F26" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B27" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C27" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D27" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E27" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F27" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B28" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C28" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D28" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E28" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F28" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B29" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C29" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D29" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E29" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F29" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B30" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C30" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D30" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E30" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F30" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B31" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C31" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D31" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="477">
   <si>
     <t>ID</t>
   </si>
@@ -359,6 +359,9 @@
     <t>16 enhanced_suspence</t>
   </si>
   <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music16)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=21</t>
   </si>
   <si>
@@ -620,6 +623,9 @@
   </si>
   <si>
     <t>5 enhanced leberch-suspense</t>
+  </si>
+  <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music5)</t>
   </si>
   <si>
     <t>源类型=type:txt_Abaddon; 层级=41</t>
@@ -800,6 +806,9 @@
   </si>
   <si>
     <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music7)</t>
   </si>
   <si>
     <t>26</t>
@@ -3711,15 +3720,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="L23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
         <v>61</v>
@@ -3737,7 +3746,7 @@
         <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3749,15 +3758,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
@@ -3775,7 +3784,7 @@
         <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3787,15 +3796,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3813,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3828,12 +3837,12 @@
         <v>28</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:12">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
@@ -3851,7 +3860,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3866,12 +3875,12 @@
         <v>23</v>
       </c>
       <c r="L27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:12">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
         <v>61</v>
@@ -3889,7 +3898,7 @@
         <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3901,15 +3910,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3927,7 +3936,7 @@
         <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3939,15 +3948,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:12">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
@@ -3965,7 +3974,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3980,12 +3989,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4003,7 +4012,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -4018,12 +4027,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:12">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
@@ -4041,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4056,12 +4065,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:12">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
@@ -4079,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4094,12 +4103,12 @@
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4117,7 +4126,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4132,12 +4141,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" ht="42" spans="1:12">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
         <v>20</v>
@@ -4155,7 +4164,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4170,12 +4179,12 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4208,12 +4217,12 @@
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" ht="90" spans="1:12">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4231,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4246,12 +4255,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
@@ -4269,7 +4278,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4284,12 +4293,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
@@ -4307,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4322,12 +4331,12 @@
         <v>23</v>
       </c>
       <c r="L39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:12">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
@@ -4345,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4360,12 +4369,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4383,7 +4392,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4398,12 +4407,12 @@
         <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4421,7 +4430,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4433,15 +4442,15 @@
         <v>15</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" ht="90" spans="1:12">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
@@ -4459,7 +4468,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4474,12 +4483,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4497,7 +4506,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4512,12 +4521,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4535,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4550,12 +4559,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
@@ -4573,7 +4582,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4588,12 +4597,12 @@
         <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -4611,7 +4620,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4626,12 +4635,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4649,12 +4658,11 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
       </c>
-      <c r="I48"/>
       <c r="J48" t="s">
         <v>15</v>
       </c>
@@ -4662,12 +4670,12 @@
         <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -4685,27 +4693,27 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
@@ -4723,7 +4731,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4735,15 +4743,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4761,7 +4769,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4776,12 +4784,12 @@
         <v>28</v>
       </c>
       <c r="L51" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" ht="55.5" spans="1:12">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
@@ -4799,7 +4807,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4811,15 +4819,15 @@
         <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" ht="90" spans="1:12">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4849,15 +4857,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L53" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" ht="150" spans="1:12">
       <c r="A54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4875,7 +4883,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4890,12 +4898,12 @@
         <v>58</v>
       </c>
       <c r="L54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
@@ -4933,7 +4941,7 @@
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4971,7 +4979,7 @@
     </row>
     <row r="57" ht="54" spans="1:12">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4989,7 +4997,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5001,15 +5009,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="150" spans="1:12">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5027,7 +5035,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5042,12 +5050,12 @@
         <v>58</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
         <v>61</v>
@@ -5085,7 +5093,7 @@
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5123,7 +5131,7 @@
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5141,7 +5149,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5153,15 +5161,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" ht="210" spans="1:12">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
@@ -5179,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5191,15 +5199,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L62" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
@@ -5217,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5232,12 +5240,12 @@
         <v>17</v>
       </c>
       <c r="L63" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
@@ -5255,7 +5263,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5275,7 +5283,7 @@
     </row>
     <row r="65" ht="54" spans="1:12">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5293,19 +5301,19 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J65" t="s">
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>15</v>
+        <v>216</v>
       </c>
       <c r="L65" t="s">
         <v>32</v>
@@ -5313,7 +5321,7 @@
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
@@ -5331,7 +5339,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5346,12 +5354,12 @@
         <v>23</v>
       </c>
       <c r="L66" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5369,7 +5377,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5389,7 +5397,7 @@
     </row>
     <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
@@ -5407,7 +5415,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5422,12 +5430,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5445,7 +5453,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5460,12 +5468,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
@@ -5483,7 +5491,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5498,12 +5506,12 @@
         <v>23</v>
       </c>
       <c r="L70" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
@@ -5521,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5536,12 +5544,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5559,7 +5567,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5574,21 +5582,21 @@
         <v>28</v>
       </c>
       <c r="L72" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5597,7 +5605,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5612,12 +5620,12 @@
         <v>23</v>
       </c>
       <c r="L73" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5626,7 +5634,7 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5635,7 +5643,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5650,12 +5658,12 @@
         <v>28</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5673,7 +5681,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5693,7 +5701,7 @@
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5723,15 +5731,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5769,7 +5777,7 @@
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5787,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5802,12 +5810,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5825,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5840,12 +5848,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
         <v>26</v>
@@ -5863,7 +5871,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5878,12 +5886,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" ht="55.5" spans="1:12">
       <c r="A81" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B81" t="s">
         <v>20</v>
@@ -5901,7 +5909,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5916,12 +5924,12 @@
         <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:12">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5939,7 +5947,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5951,7 +5959,7 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L82" t="s">
         <v>88</v>
@@ -5959,7 +5967,7 @@
     </row>
     <row r="83" ht="55.5" spans="1:12">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
@@ -5977,7 +5985,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5989,12 +5997,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B84" t="s">
         <v>26</v>
@@ -6012,7 +6020,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6027,12 +6035,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6050,7 +6058,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6065,12 +6073,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" ht="57" spans="1:12">
       <c r="A86" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6088,7 +6096,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6103,12 +6111,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
@@ -6126,7 +6134,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6138,15 +6146,15 @@
         <v>15</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L87" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
@@ -6179,12 +6187,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6202,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6217,12 +6225,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6240,7 +6248,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6255,12 +6263,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" ht="27" spans="1:12">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B91" t="s">
         <v>20</v>
@@ -6278,7 +6286,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6293,12 +6301,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B92" t="s">
         <v>61</v>
@@ -6316,7 +6324,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6331,12 +6339,12 @@
         <v>23</v>
       </c>
       <c r="L92" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" ht="54" spans="1:12">
       <c r="A93" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6354,7 +6362,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6374,7 +6382,7 @@
     </row>
     <row r="94" ht="40.5" spans="1:12">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
@@ -6392,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6407,12 +6415,12 @@
         <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
@@ -6430,7 +6438,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6442,10 +6450,10 @@
         <v>15</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L95" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -6466,39 +6474,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6506,7 +6514,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -6514,15 +6522,15 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B8" t="s">
         <v>83</v>
@@ -6530,58 +6538,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -6603,616 +6611,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B12" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C12" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E12" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F12" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B13" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D13" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B14" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D14" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B15" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D15" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B16" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C16" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D16" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E16" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F16" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B18" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C18" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D18" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B19" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C19" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E19" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B20" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C20" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D20" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E20" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B21" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C21" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E21" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F21" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B22" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D22" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E22" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C23" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E23" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F23" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B24" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C24" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D24" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E24" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F24" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B25" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C25" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D25" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E25" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F25" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B26" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C26" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E26" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B27" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C27" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E27" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F27" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B28" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" t="s">
         <v>456</v>
       </c>
-      <c r="C28" t="s">
-        <v>457</v>
-      </c>
-      <c r="D28" t="s">
-        <v>453</v>
-      </c>
       <c r="E28" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F28" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B29" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C29" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D29" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E29" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F29" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B30" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C30" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D30" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E30" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F30" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B31" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C31" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D31" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
